--- a/ProductDesign/RedDustIdeaValidationDataset.xlsx
+++ b/ProductDesign/RedDustIdeaValidationDataset.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6743"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6743" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2719" uniqueCount="1324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2803" uniqueCount="1359">
   <si>
     <t>persona_id</t>
   </si>
@@ -4001,6 +4001,111 @@
   </si>
   <si>
     <t>1 = Strongly Disagree to 5 = Strongly Agree</t>
+  </si>
+  <si>
+    <t>Do you regularly experience stress, anxiety, loneliness, low motivation, emotional overwhelm, or similar challenges in your everyday life?</t>
+  </si>
+  <si>
+    <t>Please explain why you chose this rating. What situations or experiences influenced your answer?</t>
+  </si>
+  <si>
+    <t>When you experience these challenges, do you usually have immediate access to the emotional support you need (for example, from friends, family or professionals)?</t>
+  </si>
+  <si>
+    <t>Please explain your answer. What kind of support do you currently rely on, and what do you feel is missing?</t>
+  </si>
+  <si>
+    <t>Do the digital tools and resources you currently use adequately support your overall wellbeing?</t>
+  </si>
+  <si>
+    <t>Please explain your answer. Which tools do you currently use, and what do they do well or poorly?</t>
+  </si>
+  <si>
+    <t>Would you value a digital service that understands your personal situation and provides support tailored to your individual needs?</t>
+  </si>
+  <si>
+    <t>What would personalised support mean to you? Why did you choose this rating?</t>
+  </si>
+  <si>
+    <t>Would you find it more valuable if a single digital service could both interact with you and recommend helpful content based on your situation?</t>
+  </si>
+  <si>
+    <t>What kinds of conversations or content would you find most useful?</t>
+  </si>
+  <si>
+    <t>Do you believe recommendations that consider your current mood, activity and life situation would be more useful than generic recommendations?</t>
+  </si>
+  <si>
+    <t>Can you describe situations where personalised recommendations would be helpful?</t>
+  </si>
+  <si>
+    <t>Would you feel comfortable securely sharing information such as your mood, activities or important life events if it clearly resulted in better personalised support?</t>
+  </si>
+  <si>
+    <t>What information would you be comfortable sharing, and what information would you prefer to keep private?</t>
+  </si>
+  <si>
+    <t>Would you appreciate a digital service that remembers your preferences, important life events and personal journey over time?</t>
+  </si>
+  <si>
+    <t>Why would this be valuable—or not valuable—to you?</t>
+  </si>
+  <si>
+    <t>Would seeing your wellbeing improve over time through meaningful progress tracking motivate you to build healthier habits?</t>
+  </si>
+  <si>
+    <t>What kinds of progress or achievements would you like such a service to track?</t>
+  </si>
+  <si>
+    <t>Would you prefer a digital service that adapts its support and recommendations as your life circumstances change (for example, exams, a new job, becoming a parent or retirement)?</t>
+  </si>
+  <si>
+    <t>What kinds of life changes should a service understand and adapt to?</t>
+  </si>
+  <si>
+    <t>Would you trust recommendations more if the service explained why they were suggested?</t>
+  </si>
+  <si>
+    <t>What kind of explanation would make recommendations feel trustworthy and useful?</t>
+  </si>
+  <si>
+    <t>If a digital service consistently helped you feel calmer, happier or more motivated, could you imagine using it almost every day?</t>
+  </si>
+  <si>
+    <t>What would encourage—or discourage—you from using such a service regularly?</t>
+  </si>
+  <si>
+    <t>Do you believe a helpful digital wellbeing service could become part of your everyday routine, similar to the apps you already use regularly?</t>
+  </si>
+  <si>
+    <t>What would make a wellbeing service become part of your daily routine?</t>
+  </si>
+  <si>
+    <t>If a digital wellbeing service consistently delivered meaningful value and genuinely improved your life, would you consider paying for it?</t>
+  </si>
+  <si>
+    <t>What would convince you that such a service is worth paying for? What pricing model (free, freemium, subscription, one-time purchase, etc.) would you prefer?</t>
+  </si>
+  <si>
+    <t>Do you believe there is still room for better digital services that support people's emotional wellbeing and everyday life?</t>
+  </si>
+  <si>
+    <t>What do you feel is currently missing from today's music, wellbeing or digital support services?</t>
+  </si>
+  <si>
+    <t>If you could design your ideal digital companion to support your wellbeing and everyday life, how would it help you?</t>
+  </si>
+  <si>
+    <t>Please describe the features, behaviours or experiences that would make it genuinely useful. Don't worry about current technology—imagine your ideal solution.</t>
+  </si>
+  <si>
+    <t>dream_solution</t>
+  </si>
+  <si>
+    <t>Optional</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Paragraph</t>
   </si>
 </sst>
 </file>
@@ -4160,16 +4265,10 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4181,14 +4280,8 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4201,6 +4294,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4547,129 +4652,129 @@
   </cols>
   <sheetData>
     <row r="2" spans="7:11" ht="42.4" x14ac:dyDescent="1.25">
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="15" t="s">
         <v>1227</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" spans="7:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="4" spans="7:11" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>1217</v>
       </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7" t="s">
+      <c r="H4" s="6"/>
+      <c r="I4" s="6" t="s">
         <v>1218</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>1219</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="6" t="s">
         <v>1220</v>
       </c>
     </row>
     <row r="5" spans="7:11" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="16" t="s">
         <v>1221</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="7" t="s">
         <v>1222</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="8" t="s">
         <v>1223</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="9">
         <v>46205</v>
       </c>
-      <c r="K5" s="10"/>
+      <c r="K5" s="8"/>
     </row>
     <row r="6" spans="7:11" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="G6" s="12"/>
-      <c r="H6" s="9" t="s">
+      <c r="G6" s="17"/>
+      <c r="H6" s="7" t="s">
         <v>1224</v>
       </c>
-      <c r="I6" s="13"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
     </row>
     <row r="7" spans="7:11" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="G7" s="14"/>
-      <c r="H7" s="9" t="s">
+      <c r="G7" s="18"/>
+      <c r="H7" s="7" t="s">
         <v>1225</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="8" t="s">
         <v>1226</v>
       </c>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" spans="7:11" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="G8" s="8"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" spans="7:11" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="G9" s="14"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="7:11" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="G10" s="8"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
     </row>
     <row r="11" spans="7:11" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="G11" s="14"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
     </row>
     <row r="12" spans="7:11" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="G12" s="8"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
     </row>
     <row r="13" spans="7:11" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="G13" s="14"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
     </row>
     <row r="14" spans="7:11" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="G14" s="8"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
     </row>
     <row r="15" spans="7:11" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="G15" s="14"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="G14:G15"/>
     <mergeCell ref="G2:K2"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4713,220 +4818,220 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A2" s="15">
+    <row r="2" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A2" s="11">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="11" t="s">
         <v>1271</v>
       </c>
-      <c r="C2" s="15">
-        <v>1</v>
-      </c>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="11">
+        <v>1</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>1251</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A3" s="15">
+    <row r="3" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A3" s="11">
         <v>0</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="11" t="s">
         <v>1271</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="11">
         <v>2</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="11" t="s">
         <v>1252</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="11" t="s">
         <v>1253</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A4" s="15">
-        <v>1</v>
-      </c>
-      <c r="B4" s="15" t="s">
+    <row r="4" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A4" s="11">
+        <v>1</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>1267</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="11">
         <v>3</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="11" t="s">
         <v>1268</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="11" t="s">
         <v>1269</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="11" t="s">
         <v>1233</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="11" t="s">
         <v>1270</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A5" s="15">
-        <v>1</v>
-      </c>
-      <c r="B5" s="15" t="s">
+    <row r="5" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A5" s="11">
+        <v>1</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>1267</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="11">
         <v>4</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="11" t="s">
         <v>1232</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="11" t="s">
         <v>1218</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="11" t="s">
         <v>1233</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A6" s="15">
-        <v>1</v>
-      </c>
-      <c r="B6" s="15" t="s">
+    <row r="6" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A6" s="11">
+        <v>1</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>1267</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="11">
         <v>5</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="11" t="s">
         <v>1234</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="11" t="s">
         <v>1235</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="15" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
-      <c r="A7" s="15">
-        <v>1</v>
-      </c>
-      <c r="B7" s="15" t="s">
+    <row r="7" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A7" s="11">
+        <v>1</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>1267</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="11">
         <v>6</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="11" t="s">
         <v>1237</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="11" t="s">
         <v>1236</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="11" t="s">
         <v>1238</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="11" t="s">
         <v>1239</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A8" s="15">
-        <v>1</v>
-      </c>
-      <c r="B8" s="15" t="s">
+    <row r="8" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A8" s="11">
+        <v>1</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>1267</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="11">
         <v>7</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="11" t="s">
         <v>1240</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="11" t="s">
         <v>1241</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="11" t="s">
         <v>1242</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A9" s="15">
-        <v>1</v>
-      </c>
-      <c r="B9" s="15" t="s">
+    <row r="9" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A9" s="11">
+        <v>1</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>1267</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="11">
         <v>8</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="11" t="s">
         <v>1243</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="11" t="s">
         <v>1233</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A10" s="15">
-        <v>1</v>
-      </c>
-      <c r="B10" s="15" t="s">
+    <row r="10" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A10" s="11">
+        <v>1</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>1267</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="11">
         <v>9</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="11" t="s">
         <v>1245</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="11" t="s">
         <v>1244</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="11" t="s">
         <v>1233</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="15" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
-      <c r="A11" s="15">
-        <v>1</v>
-      </c>
-      <c r="B11" s="15" t="s">
+    <row r="11" spans="1:7" s="11" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
+      <c r="A11" s="11">
+        <v>1</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>1267</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="11">
         <v>10</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="11" t="s">
         <v>1246</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="11" t="s">
         <v>1238</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="11" t="s">
         <v>1247</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A12" s="15">
+    <row r="12" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A12" s="11">
         <v>2</v>
       </c>
       <c r="B12" t="s">
         <v>1266</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="11">
         <v>11</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="11" t="s">
         <v>1255</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -4939,17 +5044,17 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A13" s="15">
+    <row r="13" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A13" s="11">
         <v>2</v>
       </c>
       <c r="B13" t="s">
         <v>1266</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="11">
         <v>12</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="11" t="s">
         <v>1259</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -4962,17 +5067,17 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A14" s="15">
+    <row r="14" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A14" s="11">
         <v>2</v>
       </c>
       <c r="B14" t="s">
         <v>1266</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="11">
         <v>13</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="11" t="s">
         <v>30</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -4985,17 +5090,17 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A15" s="15">
+    <row r="15" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A15" s="11">
         <v>2</v>
       </c>
       <c r="B15" t="s">
         <v>1266</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="11">
         <v>14</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="11" t="s">
         <v>1264</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -5008,646 +5113,1017 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="16" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A16" s="16">
+    <row r="16" spans="1:7" s="12" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A16" s="12">
         <v>3</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="13" t="s">
         <v>1272</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="12">
         <v>15</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="13" t="s">
         <v>1273</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="13" t="s">
         <v>1274</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="12" t="s">
         <v>1238</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="12" t="s">
         <v>1275</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="15" customFormat="1" ht="43.9" x14ac:dyDescent="0.45">
-      <c r="A17" s="15">
+    <row r="17" spans="1:7" s="11" customFormat="1" ht="43.9" x14ac:dyDescent="0.45">
+      <c r="A17" s="11">
         <v>3</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="14" t="s">
         <v>1272</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="11">
         <v>16</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="14" t="s">
         <v>1277</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="11" t="s">
         <v>1276</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="F17" s="11" t="s">
         <v>1238</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="11" t="s">
         <v>1278</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A18" s="15">
+    <row r="18" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A18" s="11">
         <v>3</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="14" t="s">
         <v>1272</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="11">
         <v>17</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="11" t="s">
         <v>1280</v>
       </c>
       <c r="E18" t="s">
         <v>1279</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="11" t="s">
         <v>1238</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="11" t="s">
         <v>1281</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="15" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
-      <c r="A19" s="15">
+    <row r="19" spans="1:7" s="11" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
+      <c r="A19" s="11">
         <v>3</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="14" t="s">
         <v>1272</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="11">
         <v>18</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="14" t="s">
         <v>1283</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="11" t="s">
         <v>1282</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="11" t="s">
         <v>1238</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="11" t="s">
         <v>1284</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="15" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
-      <c r="A20" s="15">
+    <row r="20" spans="1:7" s="11" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
+      <c r="A20" s="11">
         <v>3</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="14" t="s">
         <v>1272</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="11">
         <v>19</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="14" t="s">
         <v>1287</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="14" t="s">
         <v>1286</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="11" t="s">
         <v>1238</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="11" t="s">
         <v>1285</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="15" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
-      <c r="A21" s="15">
+    <row r="21" spans="1:7" s="11" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
+      <c r="A21" s="11">
         <v>4</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="11" t="s">
         <v>1288</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="11">
         <v>20</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="14" t="s">
         <v>1290</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="11" t="s">
         <v>1289</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="11" t="s">
         <v>1238</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="11" t="s">
         <v>1291</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="15" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
-      <c r="A22" s="15">
+    <row r="22" spans="1:7" s="11" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
+      <c r="A22" s="11">
         <v>5</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="14" t="s">
         <v>1292</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="11">
         <v>21</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="14" t="s">
         <v>1293</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="14" t="s">
         <v>1294</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="11" t="s">
         <v>1238</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="11" t="s">
         <v>1295</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="15" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
-      <c r="A23" s="15">
+    <row r="23" spans="1:7" s="11" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
+      <c r="A23" s="11">
         <v>6</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="11" t="s">
         <v>1296</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="11">
         <v>22</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="14" t="s">
         <v>1297</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="14" t="s">
         <v>1298</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="11" t="s">
         <v>1238</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="11" t="s">
         <v>1299</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="15" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
-      <c r="A24" s="15">
+    <row r="24" spans="1:7" s="11" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
+      <c r="A24" s="11">
         <v>7</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="11" t="s">
         <v>1300</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="11">
         <v>23</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="11" t="s">
         <v>1301</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="11" t="s">
         <v>1302</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="11" t="s">
         <v>1238</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="G24" s="11" t="s">
         <v>1303</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A25" s="15">
+    <row r="25" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A25" s="11">
         <v>7</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="11" t="s">
         <v>1300</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="11">
         <v>24</v>
       </c>
       <c r="D25" t="s">
         <v>1305</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="11" t="s">
         <v>1304</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="G25" s="11" t="s">
         <v>1306</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A26" s="15">
+    <row r="26" spans="1:7" s="11" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
+      <c r="A26" s="11">
         <v>8</v>
       </c>
       <c r="B26" t="s">
         <v>1322</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="11">
         <v>25</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="11" t="s">
         <v>1307</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>1324</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="G26" s="11" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="15" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
-      <c r="A27" s="15">
+    <row r="27" spans="1:7" s="11" customFormat="1" ht="43.9" x14ac:dyDescent="0.45">
+      <c r="A27" s="11">
         <v>8</v>
       </c>
       <c r="B27" t="s">
         <v>1322</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="11">
         <v>26</v>
       </c>
-      <c r="D27" s="15" t="s">
-        <v>1308</v>
+      <c r="E27" s="11" t="s">
+        <v>1325</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G27" s="15" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" s="15" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
-      <c r="A28" s="15">
+        <v>1358</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="11" customFormat="1" ht="73.150000000000006" x14ac:dyDescent="0.45">
+      <c r="A28" s="11">
         <v>8</v>
       </c>
       <c r="B28" t="s">
         <v>1322</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="11">
         <v>27</v>
       </c>
-      <c r="D28" s="15" t="s">
-        <v>1309</v>
+      <c r="D28" s="11" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>1326</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="G28" s="11" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="15" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
-      <c r="A29" s="15">
+    <row r="29" spans="1:7" s="11" customFormat="1" ht="43.9" x14ac:dyDescent="0.45">
+      <c r="A29" s="11">
         <v>8</v>
       </c>
       <c r="B29" t="s">
         <v>1322</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="11">
         <v>28</v>
       </c>
-      <c r="D29" s="15" t="s">
-        <v>1310</v>
+      <c r="E29" s="11" t="s">
+        <v>1327</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A30" s="15">
+        <v>1358</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="11" customFormat="1" ht="43.9" x14ac:dyDescent="0.45">
+      <c r="A30" s="11">
         <v>8</v>
       </c>
       <c r="B30" t="s">
         <v>1322</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="11">
         <v>29</v>
       </c>
-      <c r="D30" s="15" t="s">
-        <v>1311</v>
+      <c r="D30" s="11" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>1328</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="G30" s="15" t="s">
+      <c r="G30" s="11" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="15" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
-      <c r="A31" s="15">
+    <row r="31" spans="1:7" s="11" customFormat="1" ht="43.9" x14ac:dyDescent="0.45">
+      <c r="A31" s="11">
         <v>8</v>
       </c>
       <c r="B31" t="s">
         <v>1322</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="11">
         <v>30</v>
       </c>
-      <c r="D31" s="15" t="s">
-        <v>1312</v>
+      <c r="E31" s="11" t="s">
+        <v>1329</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G31" s="15" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="15" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
-      <c r="A32" s="15">
+        <v>1358</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="11" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
+      <c r="A32" s="11">
         <v>8</v>
       </c>
       <c r="B32" t="s">
         <v>1322</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="11">
         <v>31</v>
       </c>
-      <c r="D32" s="15" t="s">
-        <v>1313</v>
+      <c r="D32" s="11" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>1330</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="11" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A33" s="15">
+    <row r="33" spans="1:7" s="11" customFormat="1" ht="43.9" x14ac:dyDescent="0.45">
+      <c r="A33" s="11">
         <v>8</v>
       </c>
       <c r="B33" t="s">
         <v>1322</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="11">
         <v>32</v>
       </c>
-      <c r="D33" s="15" t="s">
-        <v>1314</v>
+      <c r="E33" s="11" t="s">
+        <v>1331</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A34" s="15">
+        <v>1358</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="11" customFormat="1" ht="73.150000000000006" x14ac:dyDescent="0.45">
+      <c r="A34" s="11">
         <v>8</v>
       </c>
       <c r="B34" t="s">
         <v>1322</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="11">
         <v>33</v>
       </c>
-      <c r="D34" s="15" t="s">
-        <v>1315</v>
+      <c r="D34" s="11" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>1332</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="G34" s="15" t="s">
+      <c r="G34" s="11" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A35" s="15">
+    <row r="35" spans="1:7" s="11" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
+      <c r="A35" s="11">
         <v>8</v>
       </c>
       <c r="B35" t="s">
         <v>1322</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="11">
         <v>34</v>
       </c>
-      <c r="D35" s="15" t="s">
-        <v>1316</v>
+      <c r="E35" s="11" t="s">
+        <v>1333</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G35" s="15" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" s="15" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
-      <c r="A36" s="15">
+        <v>1358</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="11" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
+      <c r="A36" s="11">
         <v>8</v>
       </c>
       <c r="B36" t="s">
         <v>1322</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="11">
         <v>35</v>
       </c>
-      <c r="D36" s="15" t="s">
-        <v>1317</v>
+      <c r="D36" s="11" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>1334</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="G36" s="15" t="s">
+      <c r="G36" s="11" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A37" s="15">
+    <row r="37" spans="1:7" s="11" customFormat="1" ht="43.9" x14ac:dyDescent="0.45">
+      <c r="A37" s="11">
         <v>8</v>
       </c>
       <c r="B37" t="s">
         <v>1322</v>
       </c>
-      <c r="C37" s="15">
+      <c r="C37" s="11">
         <v>36</v>
       </c>
-      <c r="D37" s="15" t="s">
-        <v>1318</v>
+      <c r="E37" s="11" t="s">
+        <v>1335</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G37" s="15" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A38" s="15">
+        <v>1358</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" s="11" customFormat="1" ht="73.150000000000006" x14ac:dyDescent="0.45">
+      <c r="A38" s="11">
         <v>8</v>
       </c>
       <c r="B38" t="s">
         <v>1322</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="11">
         <v>37</v>
       </c>
-      <c r="D38" s="15" t="s">
-        <v>1319</v>
+      <c r="D38" s="11" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>1336</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="G38" s="15" t="s">
+      <c r="G38" s="11" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="15" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
-      <c r="A39" s="15">
+    <row r="39" spans="1:7" s="11" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
+      <c r="A39" s="11">
         <v>8</v>
       </c>
       <c r="B39" t="s">
         <v>1322</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="11">
         <v>38</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>1320</v>
+      <c r="E39" s="11" t="s">
+        <v>1337</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G39" s="15" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" s="15" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
-      <c r="A40" s="15">
+        <v>1358</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="11" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
+      <c r="A40" s="11">
         <v>8</v>
       </c>
       <c r="B40" t="s">
         <v>1322</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="11">
         <v>39</v>
       </c>
-      <c r="D40" s="15" t="s">
-        <v>1321</v>
+      <c r="D40" s="11" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>1338</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="G40" s="15" t="s">
+      <c r="G40" s="11" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="42" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="43" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="44" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="45" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="46" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="47" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="48" spans="1:7" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="49" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="50" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="51" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="52" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="53" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="54" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="55" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="56" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="57" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="58" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="59" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="60" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="61" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="62" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="63" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="64" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="65" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="66" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="67" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="68" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="69" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="70" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="71" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="72" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="73" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="74" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="75" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="76" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="77" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="78" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="79" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="80" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="81" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="82" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="83" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="84" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="85" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="86" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="87" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="88" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="89" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="90" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="91" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="92" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="93" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="94" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="95" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="96" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="97" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="98" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="99" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="100" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="101" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="102" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="103" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="104" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="105" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="106" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="107" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="108" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="109" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="110" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="111" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="112" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="113" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="114" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="115" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="116" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="117" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="118" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="119" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="120" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="121" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="122" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="123" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="124" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="125" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="126" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="127" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="128" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="129" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="130" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="131" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="132" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="133" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="134" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="135" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="136" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="137" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="138" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="139" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="140" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="141" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="142" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="143" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="144" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="145" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="146" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="147" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="148" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="149" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
-    <row r="150" s="15" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="41" spans="1:7" s="11" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
+      <c r="A41" s="11">
+        <v>8</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C41" s="11">
+        <v>40</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" s="11" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
+      <c r="A42" s="11">
+        <v>8</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C42" s="11">
+        <v>41</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>1340</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" s="11" customFormat="1" ht="43.9" x14ac:dyDescent="0.45">
+      <c r="A43" s="11">
+        <v>8</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C43" s="11">
+        <v>42</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>1341</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="11" customFormat="1" ht="87.75" x14ac:dyDescent="0.45">
+      <c r="A44" s="11">
+        <v>8</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C44" s="11">
+        <v>43</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>1316</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="11" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
+      <c r="A45" s="11">
+        <v>8</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C45" s="11">
+        <v>44</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" s="11" customFormat="1" ht="43.9" x14ac:dyDescent="0.45">
+      <c r="A46" s="11">
+        <v>8</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C46" s="11">
+        <v>45</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" s="11" customFormat="1" ht="43.9" x14ac:dyDescent="0.45">
+      <c r="A47" s="11">
+        <v>8</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C47" s="11">
+        <v>46</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="11" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
+      <c r="A48" s="11">
+        <v>8</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C48" s="11">
+        <v>47</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" s="11" customFormat="1" ht="43.9" x14ac:dyDescent="0.45">
+      <c r="A49" s="11">
+        <v>8</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C49" s="11">
+        <v>48</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>1347</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" s="11" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
+      <c r="A50" s="11">
+        <v>8</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C50" s="11">
+        <v>49</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" s="11" customFormat="1" ht="29.25" x14ac:dyDescent="0.45">
+      <c r="A51" s="11">
+        <v>8</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C51" s="11">
+        <v>50</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="11" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
+      <c r="A52" s="11">
+        <v>8</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C52" s="11">
+        <v>51</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>1350</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" s="11" customFormat="1" ht="73.150000000000006" x14ac:dyDescent="0.45">
+      <c r="A53" s="11">
+        <v>8</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C53" s="11">
+        <v>52</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" s="11" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
+      <c r="A54" s="11">
+        <v>8</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C54" s="11">
+        <v>53</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" s="11" customFormat="1" ht="43.9" x14ac:dyDescent="0.45">
+      <c r="A55" s="11">
+        <v>8</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C55" s="11">
+        <v>54</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" s="11" customFormat="1" ht="58.5" x14ac:dyDescent="0.45">
+      <c r="A56" s="11">
+        <v>8</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C56" s="11">
+        <v>55</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" s="11" customFormat="1" ht="73.150000000000006" x14ac:dyDescent="0.45">
+      <c r="A57" s="11">
+        <v>8</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C57" s="11">
+        <v>56</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>1355</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="59" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="60" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="61" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="62" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="63" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="64" spans="1:7" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="65" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="66" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="67" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="68" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="69" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="70" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="71" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="72" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="73" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="74" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="75" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="76" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="77" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="78" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="79" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="80" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="81" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="82" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="83" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="84" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="85" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="86" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="87" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="88" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="89" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="90" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="91" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="92" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="93" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="94" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="95" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="96" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="97" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="98" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="99" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="100" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="101" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="102" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="103" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="104" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="105" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="106" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="107" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="108" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="109" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="110" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="111" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="112" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="113" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="114" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="115" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="116" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="117" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="118" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="119" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="120" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="121" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="122" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="123" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="124" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="125" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="126" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="127" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="128" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="129" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="130" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="131" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="132" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="133" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="134" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="135" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="136" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="137" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="138" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="139" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="140" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="141" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="142" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="143" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="144" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="145" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="146" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="147" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="148" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="149" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
+    <row r="150" s="11" customFormat="1" ht="14.65" x14ac:dyDescent="0.45"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
